--- a/artfynd/A 30203-2023 artfynd.xlsx
+++ b/artfynd/A 30203-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30203-2023 artfynd.xlsx
+++ b/artfynd/A 30203-2023 artfynd.xlsx
@@ -1383,12 +1383,7 @@
         <v>74844322</v>
       </c>
       <c r="B7" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105554</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1420,10 +1415,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>568041.0638922555</v>
+        <v>568041</v>
       </c>
       <c r="R7" t="n">
-        <v>6336163.066779934</v>
+        <v>6336163</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1453,19 +1448,9 @@
           <t>1987-01-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1991-12-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 30203-2023 artfynd.xlsx
+++ b/artfynd/A 30203-2023 artfynd.xlsx
@@ -1383,7 +1383,7 @@
         <v>74844322</v>
       </c>
       <c r="B7" t="n">
-        <v>105554</v>
+        <v>105563</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30203-2023 artfynd.xlsx
+++ b/artfynd/A 30203-2023 artfynd.xlsx
@@ -1383,7 +1383,7 @@
         <v>74844322</v>
       </c>
       <c r="B7" t="n">
-        <v>105563</v>
+        <v>105566</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30203-2023 artfynd.xlsx
+++ b/artfynd/A 30203-2023 artfynd.xlsx
@@ -1383,7 +1383,7 @@
         <v>74844322</v>
       </c>
       <c r="B7" t="n">
-        <v>105566</v>
+        <v>105594</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30203-2023 artfynd.xlsx
+++ b/artfynd/A 30203-2023 artfynd.xlsx
@@ -1383,7 +1383,7 @@
         <v>74844322</v>
       </c>
       <c r="B7" t="n">
-        <v>105594</v>
+        <v>105600</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30203-2023 artfynd.xlsx
+++ b/artfynd/A 30203-2023 artfynd.xlsx
@@ -1383,7 +1383,7 @@
         <v>74844322</v>
       </c>
       <c r="B7" t="n">
-        <v>105600</v>
+        <v>105607</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30203-2023 artfynd.xlsx
+++ b/artfynd/A 30203-2023 artfynd.xlsx
@@ -1383,7 +1383,7 @@
         <v>74844322</v>
       </c>
       <c r="B7" t="n">
-        <v>105607</v>
+        <v>105611</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30203-2023 artfynd.xlsx
+++ b/artfynd/A 30203-2023 artfynd.xlsx
@@ -1383,7 +1383,7 @@
         <v>74844322</v>
       </c>
       <c r="B7" t="n">
-        <v>105611</v>
+        <v>105618</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30203-2023 artfynd.xlsx
+++ b/artfynd/A 30203-2023 artfynd.xlsx
@@ -1383,7 +1383,7 @@
         <v>74844322</v>
       </c>
       <c r="B7" t="n">
-        <v>105621</v>
+        <v>105626</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30203-2023 artfynd.xlsx
+++ b/artfynd/A 30203-2023 artfynd.xlsx
@@ -1383,7 +1383,7 @@
         <v>74844322</v>
       </c>
       <c r="B7" t="n">
-        <v>105626</v>
+        <v>105634</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30203-2023 artfynd.xlsx
+++ b/artfynd/A 30203-2023 artfynd.xlsx
@@ -1383,7 +1383,7 @@
         <v>74844322</v>
       </c>
       <c r="B7" t="n">
-        <v>105634</v>
+        <v>105644</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30203-2023 artfynd.xlsx
+++ b/artfynd/A 30203-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>58010489</v>
+        <v>58010484</v>
       </c>
       <c r="B2" t="n">
-        <v>102164</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,14 +715,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Åsebo, Svintebo 171 m SSO vägkorset, Sm</t>
+          <t>Åsebo, Svintebo 107 m SSO vägkorset, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>568053.7226505482</v>
+        <v>567996</v>
       </c>
       <c r="R2" t="n">
-        <v>6336120.430577289</v>
+        <v>6336167</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,24 +752,14 @@
           <t>2011-02-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-02-26</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>119 cm stamomkrets</t>
+          <t>278 cm stamomkrets</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -819,12 +804,7 @@
         <v>58010485</v>
       </c>
       <c r="B3" t="n">
-        <v>102164</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>568022.0316620446</v>
+        <v>568022</v>
       </c>
       <c r="R3" t="n">
-        <v>6336163.837466735</v>
+        <v>6336164</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -898,19 +878,9 @@
           <t>2011-02-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-02-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -957,15 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>58010487</v>
+        <v>58010486</v>
       </c>
       <c r="B4" t="n">
-        <v>102164</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +957,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1002,14 +967,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åsebo, Svintebo 156 m SO vägkorset, Sm</t>
+          <t>Åsebo, Svintebo 144 m SO vägkorset, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>568058.2810058107</v>
+        <v>568051</v>
       </c>
       <c r="R4" t="n">
-        <v>6336140.572552655</v>
+        <v>6336150</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1039,24 +1004,14 @@
           <t>2011-02-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2011-02-26</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>127 cm stamomkrets</t>
+          <t>176 cm stamomkrets</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1098,15 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>58010486</v>
+        <v>58010487</v>
       </c>
       <c r="B5" t="n">
-        <v>102164</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1083,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1143,14 +1093,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åsebo, Svintebo 144 m SO vägkorset, Sm</t>
+          <t>Åsebo, Svintebo 156 m SO vägkorset, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>568051.0574396184</v>
+        <v>568058</v>
       </c>
       <c r="R5" t="n">
-        <v>6336150.215504</v>
+        <v>6336141</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1180,24 +1130,14 @@
           <t>2011-02-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2011-02-26</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>176 cm stamomkrets</t>
+          <t>127 cm stamomkrets</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1239,15 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>58010484</v>
+        <v>58010489</v>
       </c>
       <c r="B6" t="n">
-        <v>102164</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1209,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1284,14 +1219,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Åsebo, Svintebo 107 m SSO vägkorset, Sm</t>
+          <t>Åsebo, Svintebo 171 m SSO vägkorset, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567995.9012125107</v>
+        <v>568054</v>
       </c>
       <c r="R6" t="n">
-        <v>6336166.660548115</v>
+        <v>6336120</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1321,24 +1256,14 @@
           <t>2011-02-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2011-02-26</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>278 cm stamomkrets</t>
+          <t>119 cm stamomkrets</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1383,7 +1308,7 @@
         <v>74844322</v>
       </c>
       <c r="B7" t="n">
-        <v>105644</v>
+        <v>106155</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30203-2023 artfynd.xlsx
+++ b/artfynd/A 30203-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58010484</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58010485</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58010486</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,6 +1196,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58010487</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1302,6 +1327,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58010489</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1413,8 +1443,21 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74844322</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>